--- a/cour/cour_formation/UTC505/tableau convertion binaire.xlsx
+++ b/cour/cour_formation/UTC505/tableau convertion binaire.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\cour formation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SylvainTORRENTI\Documents\GitHub\PERSO-Dossier-Projet\cour\cour_formation\UTC505\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E185F9A-B0EF-41E2-A5D0-FEC867385300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3598C118-2E2A-428D-AE28-7A0E5D9AC0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{C29494EC-BAAE-4808-881E-FF870E78F5A6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C29494EC-BAAE-4808-881E-FF870E78F5A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -433,10 +433,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DCAE97-0312-4DA3-9D22-E84862C43540}">
-  <dimension ref="B3:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B3:K17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -463,6 +463,412 @@
       </c>
       <c r="J3" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>255</v>
+      </c>
+      <c r="C4">
+        <v>127</v>
+      </c>
+      <c r="D4">
+        <v>63</v>
+      </c>
+      <c r="E4">
+        <v>31</v>
+      </c>
+      <c r="F4">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>11111111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>192</v>
+      </c>
+      <c r="C6">
+        <v>64</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>224</v>
+      </c>
+      <c r="C8">
+        <v>96</v>
+      </c>
+      <c r="D8">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>11100000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>240</v>
+      </c>
+      <c r="C10">
+        <v>112</v>
+      </c>
+      <c r="D10">
+        <v>48</v>
+      </c>
+      <c r="E10">
+        <v>16</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>11110000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>248</v>
+      </c>
+      <c r="C12">
+        <v>120</v>
+      </c>
+      <c r="D12">
+        <v>56</v>
+      </c>
+      <c r="E12">
+        <v>24</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>11111000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>129</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>100000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>252</v>
+      </c>
+      <c r="C16">
+        <v>124</v>
+      </c>
+      <c r="D16">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>11111100</v>
       </c>
     </row>
   </sheetData>
